--- a/yolo.xlsx
+++ b/yolo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saintgobain-my.sharepoint.com/personal/shubham_raut2_saint-gobain_com/Documents/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B736A0-202E-4759-8323-6059FB7C0F80}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD7D18-2687-4FC9-95CA-623E3735EE20}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>this shoud not reflect</t>
+  </si>
+  <si>
+    <t>you should be grateful.</t>
   </si>
 </sst>
 </file>
@@ -80,10 +83,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -349,12 +348,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/yolo.xlsx
+++ b/yolo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saintgobain-my.sharepoint.com/personal/shubham_raut2_saint-gobain_com/Documents/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD7D18-2687-4FC9-95CA-623E3735EE20}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B588C5C-CF21-4187-BD3F-CA8CCAED01E2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>this shoud not reflect</t>
   </si>
   <si>
     <t>you should be grateful.</t>
+  </si>
+  <si>
+    <t>nikunj</t>
   </si>
 </sst>
 </file>
@@ -83,6 +86,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -348,17 +355,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G11" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/yolo.xlsx
+++ b/yolo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saintgobain-my.sharepoint.com/personal/shubham_raut2_saint-gobain_com/Documents/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B588C5C-CF21-4187-BD3F-CA8CCAED01E2}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD7D18-2687-4FC9-95CA-623E3735EE20}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>this shoud not reflect</t>
   </si>
   <si>
     <t>you should be grateful.</t>
-  </si>
-  <si>
-    <t>nikunj</t>
   </si>
 </sst>
 </file>
@@ -86,10 +83,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -355,22 +348,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G11" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/yolo.xlsx
+++ b/yolo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saintgobain-my.sharepoint.com/personal/shubham_raut2_saint-gobain_com/Documents/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD7D18-2687-4FC9-95CA-623E3735EE20}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_500D13D0D526FD753C272AFD5A4B259D6590FAB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{219742F6-AF47-4AFF-B5E7-0DB300C32DFD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>this shoud not reflect</t>
   </si>
   <si>
     <t>you should be grateful.</t>
+  </si>
+  <si>
+    <t>reset1</t>
   </si>
 </sst>
 </file>
@@ -348,17 +351,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
